--- a/data/trans_camb/P15B_tráfico-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P15B_tráfico-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,95</t>
+          <t>19,1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>10,21</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>15,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 36,32</t>
+          <t>-12,11; 36,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 41,86</t>
+          <t>-11,66; 41,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 39,07</t>
+          <t>-7,33; 39,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 50,59</t>
+          <t>-20,31; 49,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 10,8</t>
+          <t>-41,83; 11,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 29,45</t>
+          <t>-30,73; 30,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 33,77</t>
+          <t>-4,38; 34,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 21,6</t>
+          <t>-14,68; 22,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 28,13</t>
+          <t>-4,61; 30,4</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>180,31%</t>
+          <t>215,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129,86%</t>
+          <t>146,63%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,13; —</t>
+          <t>-44,52; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,42; —</t>
+          <t>-77,72; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,41; —</t>
+          <t>-29,04; —</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-67,4</t>
+          <t>-66,98</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-18,69</t>
+          <t>-19,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 28,91</t>
+          <t>-32,45; 30,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 23,56</t>
+          <t>-42,97; 24,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 39,83</t>
+          <t>-37,74; 32,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-82,74; -44,69</t>
+          <t>-84,42; -43,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-93,12; -55,05</t>
+          <t>-92,97; -54,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-81,28; -50,87</t>
+          <t>-82,25; -49,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,26; 5,14</t>
+          <t>-45,46; 3,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,08; -3,21</t>
+          <t>-58,41; -4,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 9,03</t>
+          <t>-44,61; 9,4</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-67,4%</t>
+          <t>-66,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,7%</t>
+          <t>-35,97%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,35; 219,46</t>
+          <t>-59,77; 216,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,29; 239,57</t>
+          <t>-82,29; 201,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,96; 372,87</t>
+          <t>-70,33; 240,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,74; -44,69</t>
+          <t>-84,42; -43,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-93,12; -55,05</t>
+          <t>-92,97; -54,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,28; -50,87</t>
+          <t>-82,25; -49,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,88; 13,97</t>
+          <t>-62,99; 14,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,78; -9,44</t>
+          <t>-80,97; -9,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,77; 29,27</t>
+          <t>-63,01; 35,13</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28,03</t>
+          <t>25,43</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>13,7</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22,82</t>
+          <t>21,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 34,01</t>
+          <t>2,43; 34,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 20,42</t>
+          <t>-9,22; 23,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 46,3</t>
+          <t>7,86; 43,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,69; 50,92</t>
+          <t>6,77; 58,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,36; 66,64</t>
+          <t>9,17; 65,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 33,36</t>
+          <t>0,0; 34,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 34,08</t>
+          <t>5,35; 32,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 26,82</t>
+          <t>-5,01; 25,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 39,39</t>
+          <t>6,53; 34,8</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>314,82%</t>
+          <t>285,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>301,29%</t>
+          <t>282,41%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1185,5</t>
+          <t>-15,83; 1095,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,38; 1590,03</t>
+          <t>15,8; 1311,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,82; 1344,02</t>
+          <t>2,92; 1247,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,92; 1255,89</t>
+          <t>-60,78; 966,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,37; 1577,79</t>
+          <t>25,34; 1372,33</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-19,63</t>
+          <t>-17,75</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,36</t>
+          <t>-4,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-13,69</t>
+          <t>-12,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-37,52; -0,53</t>
+          <t>-37,52; -0,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 7,45</t>
+          <t>-32,86; 8,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 1,9</t>
+          <t>-37,74; 1,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 13,56</t>
+          <t>-26,28; 14,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 23,58</t>
+          <t>-21,82; 22,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 14,18</t>
+          <t>-28,01; 13,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 0,13</t>
+          <t>-29,28; 0,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 7,56</t>
+          <t>-22,12; 8,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-29,62; -0,26</t>
+          <t>-27,34; 2,05</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-48,07%</t>
+          <t>-43,46%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-17,44%</t>
+          <t>-18,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-39,5%</t>
+          <t>-36,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,05; -1,64</t>
+          <t>-70,71; -3,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,71; 30,56</t>
+          <t>-64,44; 34,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,82; 12,61</t>
+          <t>-72,44; 7,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-69,45; 125,97</t>
+          <t>-68,18; 135,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,57; 229,25</t>
+          <t>-58,09; 193,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 118,52</t>
+          <t>-70,33; 137,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-61,89; 3,13</t>
+          <t>-63,51; 5,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 32,95</t>
+          <t>-50,64; 37,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,04; 2,57</t>
+          <t>-62,03; 9,85</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-39,36</t>
+          <t>-37,65</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-15,23</t>
+          <t>-14,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-62,5; 0,77</t>
+          <t>-65,13; 2,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-71,96; -10,04</t>
+          <t>-68,24; -9,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-67,98; -5,37</t>
+          <t>-65,83; -3,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 11,04</t>
+          <t>-26,2; 13,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 7,53</t>
+          <t>-29,88; 8,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 16,89</t>
+          <t>-23,1; 18,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-35,87; 0,17</t>
+          <t>-36,15; 0,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-40,54; -4,1</t>
+          <t>-39,01; -3,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-32,96; 3,58</t>
+          <t>-32,63; 4,58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-70,01%</t>
+          <t>-66,97%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,44%</t>
+          <t>-6,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-45,04%</t>
+          <t>-42,93%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-84,75; 3,59</t>
+          <t>-84,49; 9,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-90,6; -33,23</t>
+          <t>-90,67; -30,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-88,73; -15,03</t>
+          <t>-87,45; -15,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 163,21</t>
+          <t>-75,08; 237,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-88,1; 142,44</t>
+          <t>-87,28; 131,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,85; 251,84</t>
+          <t>-66,55; 237,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-74,45; 3,54</t>
+          <t>-73,2; 12,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-84,54; -15,8</t>
+          <t>-82,6; -14,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-71,58; 19,23</t>
+          <t>-70,4; 25,67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-8,55</t>
+          <t>-10,54</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,87</t>
+          <t>13,9</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>1,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-48,58; 10,72</t>
+          <t>-49,6; 8,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-63,13; -4,19</t>
+          <t>-59,45; -4,49</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 54,26</t>
+          <t>-56,02; 43,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 14,57</t>
+          <t>-12,99; 14,41</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 19,5</t>
+          <t>-6,88; 21,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 33,13</t>
+          <t>-1,97; 32,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 6,51</t>
+          <t>-24,92; 5,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 5,79</t>
+          <t>-23,37; 6,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 24,99</t>
+          <t>-17,87; 21,19</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-16,85%</t>
+          <t>-20,77%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>182,85%</t>
+          <t>183,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,99; 39,06</t>
+          <t>-76,07; 28,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-89,83; -3,46</t>
+          <t>-89,93; -10,95</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 213,49</t>
+          <t>-100,0; 142,39</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-67,27; —</t>
+          <t>-62,52; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-69,29; —</t>
+          <t>-61,61; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-51,04; —</t>
+          <t>-58,54; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-63,55; 50,39</t>
+          <t>-68,01; 37,79</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 50,9</t>
+          <t>-69,46; 48,27</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-59,77; 197,54</t>
+          <t>-59,91; 148,13</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-5,56</t>
+          <t>-5,24</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-3,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 3,55</t>
+          <t>-17,02; 3,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-22,82; -0,83</t>
+          <t>-21,33; 0,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 6,73</t>
+          <t>-16,47; 6,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,63</t>
+          <t>-12,59; 7,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 5,34</t>
+          <t>-14,48; 5,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 10,8</t>
+          <t>-10,18; 10,3</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 1,41</t>
+          <t>-13,9; 1,45</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -1,32</t>
+          <t>-15,62; -1,07</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 4,55</t>
+          <t>-11,18; 4,98</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-17,06%</t>
+          <t>-16,09%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-11,83%</t>
+          <t>-11,08%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 13,41</t>
+          <t>-44,18; 12,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-56,76; -2,41</t>
+          <t>-54,14; 0,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 26,69</t>
+          <t>-41,72; 23,22</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 47,86</t>
+          <t>-43,35; 55,98</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 39,07</t>
+          <t>-52,03; 35,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 71,74</t>
+          <t>-35,74; 70,2</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 6,45</t>
+          <t>-40,24; 6,74</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-48,82; -5,85</t>
+          <t>-47,93; -4,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 19,54</t>
+          <t>-34,12; 22,76</t>
         </is>
       </c>
     </row>
